--- a/sample_data.xlsx
+++ b/sample_data.xlsx
@@ -397,227 +397,205 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:E11"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>nomor_peserta</v>
+        <v>nama</v>
       </c>
       <c r="B1" t="str">
-        <v>nama_lengkap</v>
+        <v>nisn</v>
       </c>
       <c r="C1" t="str">
-        <v>ruang_ujian</v>
+        <v>kelas</v>
       </c>
       <c r="D1" t="str">
-        <v>waktu</v>
+        <v>no_peserta</v>
       </c>
       <c r="E1" t="str">
-        <v>jalur_masuk</v>
-      </c>
-      <c r="F1" t="str">
-        <v>password</v>
-      </c>
-      <c r="G1" t="str">
-        <v>nama_file_foto</v>
+        <v>ruang</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026001001</v>
+        <v>Ahmad Rizky Pratama</v>
       </c>
       <c r="B2" t="str">
-        <v>Ahmad Rizky Pratama</v>
+        <v>0078901234</v>
       </c>
       <c r="C2" t="str">
-        <v>Lab Komputer A</v>
+        <v>VI-A</v>
       </c>
       <c r="D2" t="str">
-        <v>Sesi 1 (08.00 - 10.00)</v>
+        <v>6-001</v>
       </c>
       <c r="E2" t="str">
-        <v>SNBP - Teknik Informatika</v>
-      </c>
-      <c r="F2" t="str">
-        <v>ARP2026</v>
-      </c>
-      <c r="G2" t="str">
-        <v>foto_001.svg</v>
+        <v>Ruang 1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026001002</v>
+        <v>Siti Nurhaliza Putri</v>
       </c>
       <c r="B3" t="str">
-        <v>Siti Nurhaliza Putri</v>
+        <v>0078901235</v>
       </c>
       <c r="C3" t="str">
-        <v>Lab Komputer A</v>
+        <v>VI-A</v>
       </c>
       <c r="D3" t="str">
-        <v>Sesi 1 (08.00 - 10.00)</v>
+        <v>6-002</v>
       </c>
       <c r="E3" t="str">
-        <v>SNBT - Sistem Informasi</v>
-      </c>
-      <c r="F3" t="str">
-        <v>SNP2026</v>
-      </c>
-      <c r="G3" t="str">
-        <v>foto_002.svg</v>
+        <v>Ruang 1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026001003</v>
+        <v>Budi Santoso</v>
       </c>
       <c r="B4" t="str">
-        <v>Budi Santoso</v>
+        <v>0078901236</v>
       </c>
       <c r="C4" t="str">
-        <v>Lab Komputer B</v>
+        <v>VI-A</v>
       </c>
       <c r="D4" t="str">
-        <v>Sesi 1 (08.00 - 10.00)</v>
+        <v>6-003</v>
       </c>
       <c r="E4" t="str">
-        <v>Mandiri - Teknik Elektro</v>
-      </c>
-      <c r="F4" t="str">
-        <v>BS2026</v>
-      </c>
-      <c r="G4" t="str">
-        <v>foto_003.svg</v>
+        <v>Ruang 1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026001004</v>
+        <v>Dewi Lestari Anggraini</v>
       </c>
       <c r="B5" t="str">
-        <v>Dewi Lestari Anggraini</v>
+        <v>0078901237</v>
       </c>
       <c r="C5" t="str">
-        <v>Lab Komputer B</v>
+        <v>VI-A</v>
       </c>
       <c r="D5" t="str">
-        <v>Sesi 2 (10.30 - 12.30)</v>
+        <v>6-004</v>
       </c>
       <c r="E5" t="str">
-        <v>SNBP - Manajemen</v>
-      </c>
-      <c r="F5" t="str">
-        <v>DLA2026</v>
-      </c>
-      <c r="G5" t="str">
-        <v>foto_004.svg</v>
+        <v>Ruang 1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026001005</v>
+        <v>Muhammad Farhan Hakim</v>
       </c>
       <c r="B6" t="str">
-        <v>Muhammad Farhan Hakim</v>
+        <v>0078901238</v>
       </c>
       <c r="C6" t="str">
-        <v>Lab Komputer C</v>
+        <v>VI-B</v>
       </c>
       <c r="D6" t="str">
-        <v>Sesi 2 (10.30 - 12.30)</v>
+        <v>6-005</v>
       </c>
       <c r="E6" t="str">
-        <v>SNBT - Akuntansi</v>
-      </c>
-      <c r="F6" t="str">
-        <v>MFH2026</v>
-      </c>
-      <c r="G6" t="str">
-        <v>foto_005.svg</v>
+        <v>Ruang 2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026001006</v>
+        <v>Putri Amelinda Sari</v>
       </c>
       <c r="B7" t="str">
-        <v>Putri Amelinda Sari</v>
+        <v>0078901239</v>
       </c>
       <c r="C7" t="str">
-        <v>Lab Komputer C</v>
+        <v>VI-B</v>
       </c>
       <c r="D7" t="str">
-        <v>Sesi 2 (10.30 - 12.30)</v>
+        <v>6-006</v>
       </c>
       <c r="E7" t="str">
-        <v>Mandiri - Kedokteran</v>
-      </c>
-      <c r="F7" t="str">
-        <v>PAS2026</v>
-      </c>
-      <c r="G7" t="str">
-        <v>foto_006.svg</v>
+        <v>Ruang 2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026001007</v>
+        <v>Rafi Aditya Nugroho</v>
       </c>
       <c r="B8" t="str">
-        <v>Rafi Aditya Nugroho</v>
+        <v>0078901240</v>
       </c>
       <c r="C8" t="str">
-        <v>Lab Komputer A</v>
+        <v>VI-B</v>
       </c>
       <c r="D8" t="str">
-        <v>Sesi 3 (13.00 - 15.00)</v>
+        <v>6-007</v>
       </c>
       <c r="E8" t="str">
-        <v>SNBP - Hukum</v>
-      </c>
-      <c r="F8" t="str">
-        <v>RAN2026</v>
-      </c>
-      <c r="G8" t="str">
-        <v>foto_007.svg</v>
+        <v>Ruang 2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026001008</v>
+        <v>Zahra Aulia Rahma</v>
       </c>
       <c r="B9" t="str">
-        <v>Zahra Aulia Rahma</v>
+        <v>0078901241</v>
       </c>
       <c r="C9" t="str">
-        <v>Lab Komputer A</v>
+        <v>VI-B</v>
       </c>
       <c r="D9" t="str">
-        <v>Sesi 3 (13.00 - 15.00)</v>
+        <v>6-008</v>
       </c>
       <c r="E9" t="str">
-        <v>SNBT - Psikologi</v>
-      </c>
-      <c r="F9" t="str">
-        <v>ZAR2026</v>
-      </c>
-      <c r="G9" t="str">
-        <v>foto_008.svg</v>
+        <v>Ruang 2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Dian Purnama Sari</v>
+      </c>
+      <c r="B10" t="str">
+        <v>0078901242</v>
+      </c>
+      <c r="C10" t="str">
+        <v>VI-C</v>
+      </c>
+      <c r="D10" t="str">
+        <v>6-009</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Ruang 3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Fikri Maulana Akbar</v>
+      </c>
+      <c r="B11" t="str">
+        <v>0078901243</v>
+      </c>
+      <c r="C11" t="str">
+        <v>VI-C</v>
+      </c>
+      <c r="D11" t="str">
+        <v>6-010</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Ruang 3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sample_data.xlsx
+++ b/sample_data.xlsx
@@ -442,16 +442,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Siti Nurhaliza Putri</v>
+        <v>Budi Santoso</v>
       </c>
       <c r="B3" t="str">
-        <v>0078901235</v>
+        <v>0078901236</v>
       </c>
       <c r="C3" t="str">
         <v>VI-A</v>
       </c>
       <c r="D3" t="str">
-        <v>6-002</v>
+        <v>6-003</v>
       </c>
       <c r="E3" t="str">
         <v>Ruang 1</v>
@@ -459,16 +459,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Budi Santoso</v>
+        <v>Dewi Lestari Anggraini</v>
       </c>
       <c r="B4" t="str">
-        <v>0078901236</v>
+        <v>0078901237</v>
       </c>
       <c r="C4" t="str">
         <v>VI-A</v>
       </c>
       <c r="D4" t="str">
-        <v>6-003</v>
+        <v>6-004</v>
       </c>
       <c r="E4" t="str">
         <v>Ruang 1</v>
@@ -476,50 +476,50 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Dewi Lestari Anggraini</v>
+        <v>Dian Purnama Sari</v>
       </c>
       <c r="B5" t="str">
-        <v>0078901237</v>
+        <v>0078901242</v>
       </c>
       <c r="C5" t="str">
-        <v>VI-A</v>
+        <v>VI-C</v>
       </c>
       <c r="D5" t="str">
-        <v>6-004</v>
+        <v>6-009</v>
       </c>
       <c r="E5" t="str">
-        <v>Ruang 1</v>
+        <v>Ruang 3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Muhammad Farhan Hakim</v>
+        <v>Fikri Maulana Akbar</v>
       </c>
       <c r="B6" t="str">
-        <v>0078901238</v>
+        <v>0078901243</v>
       </c>
       <c r="C6" t="str">
-        <v>VI-B</v>
+        <v>VI-C</v>
       </c>
       <c r="D6" t="str">
-        <v>6-005</v>
+        <v>6-010</v>
       </c>
       <c r="E6" t="str">
-        <v>Ruang 2</v>
+        <v>Ruang 3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Putri Amelinda Sari</v>
+        <v>Muhammad Farhan Hakim</v>
       </c>
       <c r="B7" t="str">
-        <v>0078901239</v>
+        <v>0078901238</v>
       </c>
       <c r="C7" t="str">
         <v>VI-B</v>
       </c>
       <c r="D7" t="str">
-        <v>6-006</v>
+        <v>6-005</v>
       </c>
       <c r="E7" t="str">
         <v>Ruang 2</v>
@@ -527,16 +527,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Rafi Aditya Nugroho</v>
+        <v>Putri Amelinda Sari</v>
       </c>
       <c r="B8" t="str">
-        <v>0078901240</v>
+        <v>0078901239</v>
       </c>
       <c r="C8" t="str">
         <v>VI-B</v>
       </c>
       <c r="D8" t="str">
-        <v>6-007</v>
+        <v>6-006</v>
       </c>
       <c r="E8" t="str">
         <v>Ruang 2</v>
@@ -544,16 +544,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Zahra Aulia Rahma</v>
+        <v>Rafi Aditya Nugroho</v>
       </c>
       <c r="B9" t="str">
-        <v>0078901241</v>
+        <v>0078901240</v>
       </c>
       <c r="C9" t="str">
         <v>VI-B</v>
       </c>
       <c r="D9" t="str">
-        <v>6-008</v>
+        <v>6-007</v>
       </c>
       <c r="E9" t="str">
         <v>Ruang 2</v>
@@ -561,36 +561,36 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Dian Purnama Sari</v>
+        <v>Siti Nurhaliza Putri</v>
       </c>
       <c r="B10" t="str">
-        <v>0078901242</v>
+        <v>0078901235</v>
       </c>
       <c r="C10" t="str">
-        <v>VI-C</v>
+        <v>VI-A</v>
       </c>
       <c r="D10" t="str">
-        <v>6-009</v>
+        <v>6-002</v>
       </c>
       <c r="E10" t="str">
-        <v>Ruang 3</v>
+        <v>Ruang 1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Fikri Maulana Akbar</v>
+        <v>Zahra Aulia Rahma</v>
       </c>
       <c r="B11" t="str">
-        <v>0078901243</v>
+        <v>0078901241</v>
       </c>
       <c r="C11" t="str">
-        <v>VI-C</v>
+        <v>VI-B</v>
       </c>
       <c r="D11" t="str">
-        <v>6-010</v>
+        <v>6-008</v>
       </c>
       <c r="E11" t="str">
-        <v>Ruang 3</v>
+        <v>Ruang 2</v>
       </c>
     </row>
   </sheetData>
